--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260915.xlsx
@@ -11848,7 +11848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12163,7 +12163,14 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>**※ 分母を認定者数にすると総給付費が大きく振れる。これが認定者数ベースで組めない理由である。**</t>
+          <t>**※ 見える化システムの見込量算定は「第1号被保険者数×認定率×利用率」の3段で、利用率の分母は認定者数（在宅サービスは認定者数−施設・居住系利用者数）である。**本表の「第1号被保険者1人当たり」はこの3段と代数的に同じもので、差は将来の認定率÷基準期間の認定率だけである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>**※ 小野町の認定者数は令和7年9月審査分に段差がある（961人→862人）。国保連月報で28か月を並べると、段差は認定者数にだけ現れ受給者数は連続している（認定者▲11.4％に対し受給者計▲3.9％、利用率＋8.4％）。**基準期間の令和5〜7年度はこの段差をまたぐため、認定率を3段に分解して使うと10.5％低く出る。段差の後にそろえて比べれば差は1.0％にとどまる。計上方法が確認できるまで、受給率のまま置く。</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260915.xlsx
@@ -12587,7 +12587,7 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>6569.195919846872</v>
+        <v>6570.07841765544</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−5.963％）−取崩0千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
+          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−6.148％）−取崩0千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
         </is>
       </c>
     </row>
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>6466.462150798371</v>
+        <v>6467.344648606938</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−5.963％）−取崩12,000千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
+          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−6.148％）−取崩12,000千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>6269.55576012208</v>
+        <v>6270.438257930647</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−5.963％）−取崩35,000千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
+          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−6.148％）−取崩35,000千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>**※ 調整交付金は標準給付費と総合事業費にのみかかる（包括的支援事業・任意事業費は対象外）。**見込交付割合は第9期計画の公表値から逆算した小野町の実績値5.963％を置いた。**小野町は後期高齢者加入割合が高く低所得層が厚いため、標準の5％を上回る。**第10期の値は見える化システムの係数シート（全国値）で確認する。1ptで月額295円。</t>
+          <t>**※ 調整交付金は標準給付費と総合事業費にのみかかる（包括的支援事業・任意事業費は対象外）。**見込交付割合は第9期計画の公表値から逆算した小野町の実績値6.148％を置いた。**小野町は後期高齢者加入割合が高く低所得層が厚いため、標準の5％を上回る。**第10期の値は見える化システムの係数シート（全国値）で確認する。1ptで月額295円。</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260915.xlsx
@@ -12033,26 +12033,26 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>934898.1492254316</v>
+        <v>937280.0553381076</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>931325.2900564172</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>930134.3370000789</v>
+        <v>925370.5247747266</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>928943.3839437409</v>
+        <v>919415.7594930358</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>2790403.011000237</v>
+        <v>2776111.574324179</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>-258014.862082195</v>
+        <v>-272306.2987582525</v>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>-8.46％</t>
+          <t>-8.93％</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260915.xlsx
@@ -12587,7 +12587,7 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>6570.07841765544</v>
+        <v>6401.775049971257</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−6.148％）−取崩0千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
+          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−5.533％）−取崩0千円　÷収納率99.35％÷補正後被保険者数10,245人÷12</t>
         </is>
       </c>
     </row>
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>6467.344648606938</v>
+        <v>6303.525120478659</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−6.148％）−取崩12,000千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
+          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−5.533％）−取崩12,000千円　÷収納率99.35％÷補正後被保険者数10,245人÷12</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>6270.438257930647</v>
+        <v>6115.212755617852</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−6.148％）−取崩35,000千円　÷収納率99.35％÷補正後被保険者数9,798人÷12</t>
+          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−5.533％）−取崩35,000千円　÷収納率99.35％÷補正後被保険者数10,245人÷12</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>**※ 調整交付金は標準給付費と総合事業費にのみかかる（包括的支援事業・任意事業費は対象外）。**見込交付割合は第9期計画の公表値から逆算した小野町の実績値6.148％を置いた。**小野町は後期高齢者加入割合が高く低所得層が厚いため、標準の5％を上回る。**第10期の値は見える化システムの係数シート（全国値）で確認する。1ptで月額295円。</t>
+          <t>**※ 調整交付金は標準給付費と総合事業費にのみかかる（包括的支援事業・任意事業費は対象外）。**見込交付割合は第9期計画の公表値から逆算した小野町の実績値5.533％を置いた。**小野町は後期高齢者加入割合が高く低所得層が厚いため、標準の5％を上回る。**第10期の値は見える化システムの係数シート（全国値）で確認する。1ptで月額295円。</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス別単価・見込量試算_20260915.xlsx
@@ -12185,7 +12185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -12603,11 +12603,11 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>保険料基準額（月額）　保有額12,000千円を全額取り崩す</t>
+          <t>保険料基準額（月額）　令和8年度末見込210,000千円の半分105,000千円を取り崩す</t>
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>6303.525120478659</v>
+        <v>5542.088166911039</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
@@ -12616,18 +12616,18 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−5.533％）−取崩12,000千円　÷収納率99.35％÷補正後被保険者数10,245人÷12</t>
+          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−5.533％）−取崩105,000千円　÷収納率99.35％÷補正後被保険者数10,245人÷12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>保険料基準額（月額）　第9期と同じ35,000千円を取り崩す</t>
+          <t>保険料基準額（月額）　令和8年度末見込210,000千円を全額取り崩す</t>
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>6115.212755617852</v>
+        <v>4682.401283850826</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
@@ -12636,62 +12636,82 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−5.533％）−取崩35,000千円　÷収納率99.35％÷補正後被保険者数10,245人÷12</t>
+          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−5.533％）−取崩210,000千円　÷収納率99.35％÷補正後被保険者数10,245人÷12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
+          <t>保険料基準額（月額）　第9期と同じ35,000千円を取り崩す</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n">
+        <v>6115.212755617852</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>（標準給付費3,286,398＋地域支援事業費191,749）×23％＋（標準給付費＋総合事業費103,743）×（5％−5.533％）−取崩35,000千円　÷収納率99.35％÷補正後被保険者数10,245人÷12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
           <t>第9期の保険料基準額（月額）</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B23" s="21" t="n">
         <v>6600</v>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>円</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>算定値6,886円を基金取崩により6,597円とし、100円未満切上げ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>※ 地域支援事業費は年報 様式4 の令和6年度決算（総合事業34,581千円＋包括的支援事業・任意事業29,335千円）を3年度とも据え置き、3年計191,749千円（うち総合事業費103,743千円）とした。令和7年度は年報が未入力のため取れない。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>※ 第1号被保険者負担割合は第9期と同じ23％。**3年の計画期間ごとに政令で定められるもので、第10期の値は確認を要する。1ptで月額303円。**</t>
+          <t>※ 地域支援事業費は年報 様式4 の令和6年度決算（総合事業34,581千円＋包括的支援事業・任意事業29,335千円）を3年度とも据え置き、3年計191,749千円（うち総合事業費103,743千円）とした。令和7年度は年報が未入力のため取れない。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>**※ 調整交付金は標準給付費と総合事業費にのみかかる（包括的支援事業・任意事業費は対象外）。**見込交付割合は第9期計画の公表値から逆算した小野町の実績値5.533％を置いた。**小野町は後期高齢者加入割合が高く低所得層が厚いため、標準の5％を上回る。**第10期の値は見える化システムの係数シート（全国値）で確認する。1ptで月額295円。</t>
+          <t>※ 第1号被保険者負担割合は第9期と同じ23％。**3年の計画期間ごとに政令で定められるもので、第10期の値は確認を要する。1ptで月額303円。**</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>※ 補正後被保険者数は、令和7年度末の所得段階別構成比（様式1 所得段階別）を第10期3年分の第1号被保険者数10,284人に当てたもの。所得段階の設定が変われば動く。</t>
+          <t>**※ 調整交付金は標準給付費と総合事業費にのみかかる（包括的支援事業・任意事業費は対象外）。**見込交付割合は第9期計画の公表値から逆算した小野町の実績値5.533％を置いた。**小野町は後期高齢者加入割合が高く低所得層が厚いため、標準の5％を上回る。**第10期の値は見える化システムの係数シート（全国値）で確認する。1ptで月額295円。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>**※ 準備基金の保有額は令和5・6年度末とも12,000千円である。第9期が見込んだ35,000千円の取崩は、この残高では実行できない。残高の確認が第10期の保険料算定の前提となる。**</t>
+          <t>※ 補正後被保険者数は、令和7年度末の所得段階別構成比（様式1 所得段階別）を第10期3年分の第1号被保険者数10,284人に当てたもの。所得段階の設定が変われば動く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>**※ 準備基金の残高は令和5年度末120,000千円（町の財務書類）、令和8年度末見込210,000千円。第9期が見込んだ35,000千円の取崩は、残高の範囲内で実行できる。取崩額は町と協議会で決める。**</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13128,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>12,000（保有額）</t>
+          <t>120,000（令和5年度末残高）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
@@ -13121,7 +13141,7 @@
       <c r="K11" s="6" t="inlineStr"/>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>**令和5・6年度末の基金保有額はいずれも12,000千円。令和4年度末の120,000千円から1桁減っている。取崩実績か入力誤りかの確認を要する**</t>
+          <t>**残高は令和5年度末120,000千円（町の財務書類）、令和8年度末見込210,000千円。取崩しは令和2年度以降なし。年報 様式4 の保有額は財務書類と合わない**</t>
         </is>
       </c>
     </row>
